--- a/Experiment/Orders/PAR27_RUN05.xlsx
+++ b/Experiment/Orders/PAR27_RUN05.xlsx
@@ -30,312 +30,312 @@
     <t>2D_Object</t>
   </si>
   <si>
+    <t>3D_Hand</t>
+  </si>
+  <si>
+    <t>3D_Object</t>
+  </si>
+  <si>
+    <t>3D_Face</t>
+  </si>
+  <si>
     <t>2D_Face</t>
   </si>
   <si>
-    <t>3D_Face</t>
-  </si>
-  <si>
-    <t>3D_Object</t>
-  </si>
-  <si>
-    <t>3D_Hand</t>
-  </si>
-  <si>
     <t>Duration_Seconds</t>
   </si>
   <si>
     <t>Filename_left</t>
   </si>
   <si>
+    <t>Hand_15_R.png</t>
+  </si>
+  <si>
+    <t>Object_14_R.png</t>
+  </si>
+  <si>
+    <t>Hand_04_L.png</t>
+  </si>
+  <si>
+    <t>Object_11_R.png</t>
+  </si>
+  <si>
+    <t>Object_04_L.png</t>
+  </si>
+  <si>
+    <t>Face_08_L.png</t>
+  </si>
+  <si>
+    <t>Face_09_L.png</t>
+  </si>
+  <si>
+    <t>Object_07_L.png</t>
+  </si>
+  <si>
+    <t>Hand_02_R.png</t>
+  </si>
+  <si>
+    <t>Face_06_R.png</t>
+  </si>
+  <si>
+    <t>Hand_02_L.png</t>
+  </si>
+  <si>
+    <t>Hand_04_R.png</t>
+  </si>
+  <si>
+    <t>Object_01_L.png</t>
+  </si>
+  <si>
+    <t>Object_13_R.png</t>
+  </si>
+  <si>
+    <t>Hand_10_R.png</t>
+  </si>
+  <si>
+    <t>Hand_08_L.png</t>
+  </si>
+  <si>
+    <t>Face_11_L.png</t>
+  </si>
+  <si>
+    <t>Hand_16_R.png</t>
+  </si>
+  <si>
+    <t>Hand_12_R.png</t>
+  </si>
+  <si>
+    <t>Face_04_L.png</t>
+  </si>
+  <si>
+    <t>Face_10_R.png</t>
+  </si>
+  <si>
+    <t>Object_08_R.png</t>
+  </si>
+  <si>
+    <t>Face_16_R.png</t>
+  </si>
+  <si>
+    <t>Hand_11_R.png</t>
+  </si>
+  <si>
+    <t>Face_12_L.png</t>
+  </si>
+  <si>
+    <t>Object_15_R.png</t>
+  </si>
+  <si>
+    <t>Object_07_R.png</t>
+  </si>
+  <si>
+    <t>Face_02_L.png</t>
+  </si>
+  <si>
+    <t>Hand_16_L.png</t>
+  </si>
+  <si>
+    <t>Face_09_R.png</t>
+  </si>
+  <si>
+    <t>Face_05_L.png</t>
+  </si>
+  <si>
+    <t>Face_10_L.png</t>
+  </si>
+  <si>
+    <t>Object_11_L.png</t>
+  </si>
+  <si>
+    <t>Face_01_R.png</t>
+  </si>
+  <si>
+    <t>Face_03_R.png</t>
+  </si>
+  <si>
+    <t>Object_10_L.png</t>
+  </si>
+  <si>
+    <t>Hand_14_L.png</t>
+  </si>
+  <si>
+    <t>Hand_07_L.png</t>
+  </si>
+  <si>
+    <t>Object_14_L.png</t>
+  </si>
+  <si>
+    <t>Object_13_L.png</t>
+  </si>
+  <si>
+    <t>Object_08_L.png</t>
+  </si>
+  <si>
+    <t>Face_11_R.png</t>
+  </si>
+  <si>
+    <t>Face_03_L.png</t>
+  </si>
+  <si>
+    <t>Face_13_R.png</t>
+  </si>
+  <si>
+    <t>Object_09_R.png</t>
+  </si>
+  <si>
+    <t>Hand_03_L.png</t>
+  </si>
+  <si>
+    <t>Hand_03_R.png</t>
+  </si>
+  <si>
+    <t>Object_16_L.png</t>
+  </si>
+  <si>
+    <t>Face_06_L.png</t>
+  </si>
+  <si>
+    <t>Hand_13_R.png</t>
+  </si>
+  <si>
+    <t>Object_01_R.png</t>
+  </si>
+  <si>
+    <t>Object_05_L.png</t>
+  </si>
+  <si>
+    <t>Object_04_R.png</t>
+  </si>
+  <si>
+    <t>Hand_07_R.png</t>
+  </si>
+  <si>
+    <t>Face_15_R.png</t>
+  </si>
+  <si>
+    <t>Hand_10_L.png</t>
+  </si>
+  <si>
+    <t>Object_03_R.png</t>
+  </si>
+  <si>
+    <t>Object_06_R.png</t>
+  </si>
+  <si>
+    <t>Face_07_R.png</t>
+  </si>
+  <si>
+    <t>Object_02_L.png</t>
+  </si>
+  <si>
+    <t>Hand_05_L.png</t>
+  </si>
+  <si>
+    <t>Object_12_L.png</t>
+  </si>
+  <si>
+    <t>Hand_09_R.png</t>
+  </si>
+  <si>
+    <t>Hand_09_L.png</t>
+  </si>
+  <si>
+    <t>Hand_11_L.png</t>
+  </si>
+  <si>
+    <t>Face_04_R.png</t>
+  </si>
+  <si>
+    <t>Face_05_R.png</t>
+  </si>
+  <si>
+    <t>Hand_01_R.png</t>
+  </si>
+  <si>
+    <t>Hand_06_R.png</t>
+  </si>
+  <si>
+    <t>Hand_12_L.png</t>
+  </si>
+  <si>
+    <t>Face_16_L.png</t>
+  </si>
+  <si>
+    <t>Hand_01_L.png</t>
+  </si>
+  <si>
+    <t>Object_09_L.png</t>
+  </si>
+  <si>
+    <t>Face_08_R.png</t>
+  </si>
+  <si>
+    <t>Hand_13_L.png</t>
+  </si>
+  <si>
+    <t>Face_02_R.png</t>
+  </si>
+  <si>
+    <t>Object_03_L.png</t>
+  </si>
+  <si>
+    <t>Hand_06_L.png</t>
+  </si>
+  <si>
+    <t>Object_10_R.png</t>
+  </si>
+  <si>
+    <t>Face_15_L.png</t>
+  </si>
+  <si>
+    <t>Object_02_R.png</t>
+  </si>
+  <si>
+    <t>Hand_15_L.png</t>
+  </si>
+  <si>
+    <t>Face_13_L.png</t>
+  </si>
+  <si>
+    <t>Object_05_R.png</t>
+  </si>
+  <si>
+    <t>Face_07_L.png</t>
+  </si>
+  <si>
+    <t>Face_14_R.png</t>
+  </si>
+  <si>
+    <t>Face_01_L.png</t>
+  </si>
+  <si>
+    <t>Hand_05_R.png</t>
+  </si>
+  <si>
+    <t>Face_12_R.png</t>
+  </si>
+  <si>
+    <t>Object_16_R.png</t>
+  </si>
+  <si>
+    <t>Object_06_L.png</t>
+  </si>
+  <si>
+    <t>Object_12_R.png</t>
+  </si>
+  <si>
+    <t>Hand_14_R.png</t>
+  </si>
+  <si>
+    <t>Face_14_L.png</t>
+  </si>
+  <si>
+    <t>Object_15_L.png</t>
+  </si>
+  <si>
     <t>Hand_08_R.png</t>
   </si>
   <si>
-    <t>Object_03_R.png</t>
-  </si>
-  <si>
-    <t>Face_10_R.png</t>
-  </si>
-  <si>
-    <t>Face_12_L.png</t>
-  </si>
-  <si>
-    <t>Object_13_R.png</t>
-  </si>
-  <si>
-    <t>Face_07_L.png</t>
-  </si>
-  <si>
-    <t>Face_06_L.png</t>
-  </si>
-  <si>
-    <t>Face_11_R.png</t>
-  </si>
-  <si>
-    <t>Object_02_L.png</t>
-  </si>
-  <si>
-    <t>Face_10_L.png</t>
-  </si>
-  <si>
-    <t>Hand_07_L.png</t>
-  </si>
-  <si>
-    <t>Hand_11_L.png</t>
-  </si>
-  <si>
-    <t>Object_01_R.png</t>
-  </si>
-  <si>
-    <t>Object_01_L.png</t>
-  </si>
-  <si>
-    <t>Hand_05_L.png</t>
-  </si>
-  <si>
-    <t>Face_08_R.png</t>
-  </si>
-  <si>
-    <t>Face_16_R.png</t>
-  </si>
-  <si>
-    <t>Hand_14_L.png</t>
-  </si>
-  <si>
-    <t>Hand_13_R.png</t>
-  </si>
-  <si>
-    <t>Face_11_L.png</t>
-  </si>
-  <si>
-    <t>Object_06_L.png</t>
-  </si>
-  <si>
-    <t>Object_07_R.png</t>
-  </si>
-  <si>
-    <t>Hand_09_L.png</t>
-  </si>
-  <si>
-    <t>Object_04_L.png</t>
-  </si>
-  <si>
-    <t>Face_14_R.png</t>
-  </si>
-  <si>
-    <t>Object_14_R.png</t>
-  </si>
-  <si>
-    <t>Object_09_R.png</t>
-  </si>
-  <si>
-    <t>Hand_16_R.png</t>
-  </si>
-  <si>
-    <t>Face_05_R.png</t>
-  </si>
-  <si>
-    <t>Hand_01_R.png</t>
-  </si>
-  <si>
-    <t>Object_08_L.png</t>
-  </si>
-  <si>
-    <t>Object_03_L.png</t>
-  </si>
-  <si>
-    <t>Hand_03_R.png</t>
-  </si>
-  <si>
-    <t>Hand_02_L.png</t>
-  </si>
-  <si>
-    <t>Face_15_L.png</t>
-  </si>
-  <si>
-    <t>Hand_15_R.png</t>
-  </si>
-  <si>
-    <t>Hand_12_R.png</t>
-  </si>
-  <si>
-    <t>Face_14_L.png</t>
-  </si>
-  <si>
-    <t>Face_04_R.png</t>
-  </si>
-  <si>
-    <t>Face_09_L.png</t>
-  </si>
-  <si>
-    <t>Object_16_R.png</t>
-  </si>
-  <si>
-    <t>Object_07_L.png</t>
-  </si>
-  <si>
-    <t>Face_03_R.png</t>
-  </si>
-  <si>
-    <t>Hand_03_L.png</t>
-  </si>
-  <si>
-    <t>Hand_02_R.png</t>
-  </si>
-  <si>
-    <t>Object_14_L.png</t>
-  </si>
-  <si>
-    <t>Hand_10_L.png</t>
-  </si>
-  <si>
-    <t>Object_10_L.png</t>
-  </si>
-  <si>
-    <t>Hand_07_R.png</t>
-  </si>
-  <si>
-    <t>Object_12_R.png</t>
-  </si>
-  <si>
-    <t>Face_16_L.png</t>
-  </si>
-  <si>
-    <t>Face_02_L.png</t>
-  </si>
-  <si>
-    <t>Hand_16_L.png</t>
-  </si>
-  <si>
-    <t>Object_10_R.png</t>
-  </si>
-  <si>
-    <t>Hand_13_L.png</t>
-  </si>
-  <si>
-    <t>Face_02_R.png</t>
-  </si>
-  <si>
-    <t>Hand_09_R.png</t>
-  </si>
-  <si>
-    <t>Hand_08_L.png</t>
-  </si>
-  <si>
-    <t>Hand_06_L.png</t>
-  </si>
-  <si>
-    <t>Face_13_L.png</t>
-  </si>
-  <si>
-    <t>Object_12_L.png</t>
-  </si>
-  <si>
-    <t>Object_11_R.png</t>
-  </si>
-  <si>
-    <t>Object_04_R.png</t>
-  </si>
-  <si>
-    <t>Face_06_R.png</t>
-  </si>
-  <si>
-    <t>Face_12_R.png</t>
-  </si>
-  <si>
-    <t>Object_06_R.png</t>
-  </si>
-  <si>
-    <t>Hand_14_R.png</t>
-  </si>
-  <si>
-    <t>Face_13_R.png</t>
-  </si>
-  <si>
-    <t>Object_16_L.png</t>
-  </si>
-  <si>
-    <t>Face_05_L.png</t>
-  </si>
-  <si>
-    <t>Hand_04_R.png</t>
-  </si>
-  <si>
-    <t>Hand_11_R.png</t>
-  </si>
-  <si>
-    <t>Face_15_R.png</t>
-  </si>
-  <si>
-    <t>Object_05_R.png</t>
-  </si>
-  <si>
-    <t>Object_09_L.png</t>
-  </si>
-  <si>
-    <t>Object_13_L.png</t>
-  </si>
-  <si>
-    <t>Hand_06_R.png</t>
-  </si>
-  <si>
-    <t>Object_05_L.png</t>
-  </si>
-  <si>
-    <t>Face_07_R.png</t>
-  </si>
-  <si>
-    <t>Hand_04_L.png</t>
-  </si>
-  <si>
-    <t>Object_15_R.png</t>
-  </si>
-  <si>
-    <t>Face_04_L.png</t>
-  </si>
-  <si>
-    <t>Hand_05_R.png</t>
-  </si>
-  <si>
-    <t>Face_01_L.png</t>
-  </si>
-  <si>
-    <t>Hand_12_L.png</t>
-  </si>
-  <si>
-    <t>Object_15_L.png</t>
-  </si>
-  <si>
-    <t>Hand_15_L.png</t>
-  </si>
-  <si>
-    <t>Face_08_L.png</t>
-  </si>
-  <si>
-    <t>Object_02_R.png</t>
-  </si>
-  <si>
-    <t>Hand_10_R.png</t>
-  </si>
-  <si>
-    <t>Object_08_R.png</t>
-  </si>
-  <si>
-    <t>Hand_01_L.png</t>
-  </si>
-  <si>
-    <t>Face_09_R.png</t>
-  </si>
-  <si>
-    <t>Face_03_L.png</t>
-  </si>
-  <si>
-    <t>Face_01_R.png</t>
-  </si>
-  <si>
-    <t>Object_11_L.png</t>
-  </si>
-  <si>
     <t>Filename_right</t>
   </si>
   <si>
@@ -384,52 +384,52 @@
     <t>0</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>08</t>
   </si>
   <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
     <t>03</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>15</t>
   </si>
 </sst>
 </file>
@@ -666,7 +666,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D6" s="0"/>
       <c r="E6" s="0"/>
@@ -700,7 +700,7 @@
         <v>13</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F7" s="0" t="s">
         <v>109</v>
@@ -713,10 +713,10 @@
         <v>113</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K7" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L7" s="0" t="s">
         <v>125</v>
@@ -730,7 +730,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D8" s="0"/>
       <c r="E8" s="0"/>
@@ -755,7 +755,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C9" s="0">
         <v>1</v>
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="F9" s="0" t="s">
         <v>109</v>
@@ -777,10 +777,10 @@
         <v>113</v>
       </c>
       <c r="J9" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K9" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L9" s="0" t="s">
         <v>126</v>
@@ -819,7 +819,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C11" s="0">
         <v>1</v>
@@ -828,7 +828,7 @@
         <v>15</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="F11" s="0" t="s">
         <v>109</v>
@@ -841,13 +841,13 @@
         <v>113</v>
       </c>
       <c r="J11" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K11" s="0" t="s">
         <v>119</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12">
@@ -883,7 +883,7 @@
         <v>6</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" s="0">
         <v>1</v>
@@ -892,7 +892,7 @@
         <v>16</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F13" s="0" t="s">
         <v>109</v>
@@ -911,7 +911,7 @@
         <v>120</v>
       </c>
       <c r="L13" s="0" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -922,7 +922,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D14" s="0"/>
       <c r="E14" s="0"/>
@@ -947,7 +947,7 @@
         <v>7</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15" s="0">
         <v>1</v>
@@ -956,7 +956,7 @@
         <v>17</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="F15" s="0" t="s">
         <v>109</v>
@@ -975,7 +975,7 @@
         <v>120</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16">
@@ -1011,7 +1011,7 @@
         <v>8</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" s="0">
         <v>1</v>
@@ -1020,7 +1020,7 @@
         <v>18</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F17" s="0" t="s">
         <v>109</v>
@@ -1033,13 +1033,13 @@
         <v>113</v>
       </c>
       <c r="J17" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K17" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L17" s="0" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18">
@@ -1050,7 +1050,7 @@
         <v>2</v>
       </c>
       <c r="C18" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D18" s="0"/>
       <c r="E18" s="0"/>
@@ -1075,7 +1075,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C19" s="0">
         <v>1</v>
@@ -1084,7 +1084,7 @@
         <v>19</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="F19" s="0" t="s">
         <v>109</v>
@@ -1097,13 +1097,13 @@
         <v>113</v>
       </c>
       <c r="J19" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K19" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L19" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20">
@@ -1139,7 +1139,7 @@
         <v>10</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C21" s="0">
         <v>1</v>
@@ -1148,7 +1148,7 @@
         <v>20</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F21" s="0" t="s">
         <v>109</v>
@@ -1161,13 +1161,13 @@
         <v>113</v>
       </c>
       <c r="J21" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K21" s="0" t="s">
         <v>120</v>
       </c>
       <c r="L21" s="0" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22">
@@ -1178,7 +1178,7 @@
         <v>2</v>
       </c>
       <c r="C22" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D22" s="0"/>
       <c r="E22" s="0"/>
@@ -1203,7 +1203,7 @@
         <v>11</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C23" s="0">
         <v>1</v>
@@ -1212,7 +1212,7 @@
         <v>21</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="F23" s="0" t="s">
         <v>109</v>
@@ -1231,7 +1231,7 @@
         <v>118</v>
       </c>
       <c r="L23" s="0" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24">
@@ -1267,7 +1267,7 @@
         <v>12</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C25" s="0">
         <v>1</v>
@@ -1276,7 +1276,7 @@
         <v>22</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="F25" s="0" t="s">
         <v>109</v>
@@ -1289,13 +1289,13 @@
         <v>113</v>
       </c>
       <c r="J25" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K25" s="0" t="s">
         <v>118</v>
       </c>
       <c r="L25" s="0" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26">
@@ -1306,7 +1306,7 @@
         <v>2</v>
       </c>
       <c r="C26" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D26" s="0"/>
       <c r="E26" s="0"/>
@@ -1331,7 +1331,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C27" s="0">
         <v>1</v>
@@ -1340,7 +1340,7 @@
         <v>23</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="F27" s="0" t="s">
         <v>109</v>
@@ -1353,7 +1353,7 @@
         <v>113</v>
       </c>
       <c r="J27" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K27" s="0" t="s">
         <v>119</v>
@@ -1395,7 +1395,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C29" s="0">
         <v>1</v>
@@ -1404,7 +1404,7 @@
         <v>24</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F29" s="0" t="s">
         <v>109</v>
@@ -1417,13 +1417,13 @@
         <v>113</v>
       </c>
       <c r="J29" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K29" s="0" t="s">
         <v>119</v>
       </c>
       <c r="L29" s="0" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30">
@@ -1459,7 +1459,7 @@
         <v>15</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C31" s="0">
         <v>1</v>
@@ -1468,7 +1468,7 @@
         <v>25</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="F31" s="0" t="s">
         <v>109</v>
@@ -1481,13 +1481,13 @@
         <v>113</v>
       </c>
       <c r="J31" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K31" s="0" t="s">
         <v>118</v>
       </c>
       <c r="L31" s="0" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32">
@@ -1498,7 +1498,7 @@
         <v>2</v>
       </c>
       <c r="C32" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D32" s="0"/>
       <c r="E32" s="0"/>
@@ -1532,7 +1532,7 @@
         <v>26</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="F33" s="0" t="s">
         <v>109</v>
@@ -1545,13 +1545,13 @@
         <v>113</v>
       </c>
       <c r="J33" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K33" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L33" s="0" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34">
@@ -1587,7 +1587,7 @@
         <v>17</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C35" s="0">
         <v>1</v>
@@ -1596,7 +1596,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="F35" s="0" t="s">
         <v>109</v>
@@ -1609,13 +1609,13 @@
         <v>113</v>
       </c>
       <c r="J35" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K35" s="0" t="s">
         <v>120</v>
       </c>
       <c r="L35" s="0" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36">
@@ -1651,7 +1651,7 @@
         <v>18</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C37" s="0">
         <v>1</v>
@@ -1660,7 +1660,7 @@
         <v>28</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="F37" s="0" t="s">
         <v>109</v>
@@ -1673,7 +1673,7 @@
         <v>113</v>
       </c>
       <c r="J37" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K37" s="0" t="s">
         <v>118</v>
@@ -1743,7 +1743,7 @@
         <v>118</v>
       </c>
       <c r="L39" s="0" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40">
@@ -1779,7 +1779,7 @@
         <v>20</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C41" s="0">
         <v>1</v>
@@ -1788,7 +1788,7 @@
         <v>30</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="F41" s="0" t="s">
         <v>109</v>
@@ -1807,7 +1807,7 @@
         <v>120</v>
       </c>
       <c r="L41" s="0" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42">
@@ -1818,7 +1818,7 @@
         <v>2</v>
       </c>
       <c r="C42" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D42" s="0"/>
       <c r="E42" s="0"/>
@@ -1843,7 +1843,7 @@
         <v>21</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C43" s="0">
         <v>1</v>
@@ -1852,7 +1852,7 @@
         <v>31</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="F43" s="0" t="s">
         <v>109</v>
@@ -1865,13 +1865,13 @@
         <v>113</v>
       </c>
       <c r="J43" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K43" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L43" s="0" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="44">
@@ -1935,7 +1935,7 @@
         <v>119</v>
       </c>
       <c r="L45" s="0" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="46">
@@ -1946,7 +1946,7 @@
         <v>2</v>
       </c>
       <c r="C46" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D46" s="0"/>
       <c r="E46" s="0"/>
@@ -1980,7 +1980,7 @@
         <v>33</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="F47" s="0" t="s">
         <v>109</v>
@@ -1993,13 +1993,13 @@
         <v>113</v>
       </c>
       <c r="J47" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K47" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L47" s="0" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="48">
@@ -2035,7 +2035,7 @@
         <v>24</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C49" s="0">
         <v>1</v>
@@ -2044,7 +2044,7 @@
         <v>34</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="F49" s="0" t="s">
         <v>109</v>
@@ -2057,13 +2057,13 @@
         <v>113</v>
       </c>
       <c r="J49" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K49" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L49" s="0" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
     </row>
     <row r="50">
@@ -2074,7 +2074,7 @@
         <v>2</v>
       </c>
       <c r="C50" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D50" s="0"/>
       <c r="E50" s="0"/>
@@ -2099,7 +2099,7 @@
         <v>25</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C51" s="0">
         <v>1</v>
@@ -2108,7 +2108,7 @@
         <v>35</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="F51" s="0" t="s">
         <v>109</v>
@@ -2121,13 +2121,13 @@
         <v>113</v>
       </c>
       <c r="J51" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K51" s="0" t="s">
         <v>120</v>
       </c>
       <c r="L51" s="0" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="52">
@@ -2138,7 +2138,7 @@
         <v>2</v>
       </c>
       <c r="C52" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D52" s="0"/>
       <c r="E52" s="0"/>
@@ -2191,7 +2191,7 @@
         <v>119</v>
       </c>
       <c r="L53" s="0" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
     </row>
     <row r="54">
@@ -2202,7 +2202,7 @@
         <v>2</v>
       </c>
       <c r="C54" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D54" s="0"/>
       <c r="E54" s="0"/>
@@ -2255,7 +2255,7 @@
         <v>119</v>
       </c>
       <c r="L55" s="0" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56">
@@ -2291,7 +2291,7 @@
         <v>28</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C57" s="0">
         <v>1</v>
@@ -2300,7 +2300,7 @@
         <v>38</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="F57" s="0" t="s">
         <v>109</v>
@@ -2313,13 +2313,13 @@
         <v>113</v>
       </c>
       <c r="J57" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K57" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L57" s="0" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="58">
@@ -2364,7 +2364,7 @@
         <v>39</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="F59" s="0" t="s">
         <v>109</v>
@@ -2377,13 +2377,13 @@
         <v>113</v>
       </c>
       <c r="J59" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K59" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="60">
@@ -2394,7 +2394,7 @@
         <v>2</v>
       </c>
       <c r="C60" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D60" s="0"/>
       <c r="E60" s="0"/>
@@ -2419,7 +2419,7 @@
         <v>30</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C61" s="0">
         <v>1</v>
@@ -2444,10 +2444,10 @@
         <v>115</v>
       </c>
       <c r="K61" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L61" s="0" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="62">
@@ -2492,7 +2492,7 @@
         <v>41</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="F63" s="0" t="s">
         <v>109</v>
@@ -2508,10 +2508,10 @@
         <v>116</v>
       </c>
       <c r="K63" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L63" s="0" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
     </row>
     <row r="64">
@@ -2556,7 +2556,7 @@
         <v>42</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F65" s="0" t="s">
         <v>109</v>
@@ -2572,10 +2572,10 @@
         <v>116</v>
       </c>
       <c r="K65" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
     <row r="66">
@@ -2586,7 +2586,7 @@
         <v>2</v>
       </c>
       <c r="C66" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D66" s="0"/>
       <c r="E66" s="0"/>
@@ -2611,7 +2611,7 @@
         <v>33</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C67" s="0">
         <v>1</v>
@@ -2620,7 +2620,7 @@
         <v>43</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="F67" s="0" t="s">
         <v>109</v>
@@ -2633,13 +2633,13 @@
         <v>113</v>
       </c>
       <c r="J67" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K67" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L67" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="68">
@@ -2650,7 +2650,7 @@
         <v>2</v>
       </c>
       <c r="C68" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D68" s="0"/>
       <c r="E68" s="0"/>
@@ -2684,7 +2684,7 @@
         <v>44</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="F69" s="0" t="s">
         <v>109</v>
@@ -2697,13 +2697,13 @@
         <v>113</v>
       </c>
       <c r="J69" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K69" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="70">
@@ -2739,7 +2739,7 @@
         <v>35</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C71" s="0">
         <v>1</v>
@@ -2748,7 +2748,7 @@
         <v>45</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="F71" s="0" t="s">
         <v>109</v>
@@ -2761,7 +2761,7 @@
         <v>113</v>
       </c>
       <c r="J71" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K71" s="0" t="s">
         <v>120</v>
@@ -2778,7 +2778,7 @@
         <v>2</v>
       </c>
       <c r="C72" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D72" s="0"/>
       <c r="E72" s="0"/>
@@ -2809,16 +2809,16 @@
         <v>1</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F73" s="0" t="s">
         <v>109</v>
       </c>
       <c r="G73" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" s="0"/>
       <c r="I73" s="0" t="s">
@@ -2828,10 +2828,10 @@
         <v>116</v>
       </c>
       <c r="K73" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L73" s="0" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="74">
@@ -2842,7 +2842,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D74" s="0"/>
       <c r="E74" s="0"/>
@@ -2867,16 +2867,16 @@
         <v>37</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C75" s="0">
         <v>1</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>46</v>
+        <v>103</v>
       </c>
       <c r="F75" s="0" t="s">
         <v>109</v>
@@ -2889,13 +2889,13 @@
         <v>113</v>
       </c>
       <c r="J75" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K75" s="0" t="s">
         <v>118</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76">
@@ -2931,7 +2931,7 @@
         <v>38</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C77" s="0">
         <v>1</v>
@@ -2940,26 +2940,26 @@
         <v>47</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>47</v>
+        <v>103</v>
       </c>
       <c r="F77" s="0" t="s">
         <v>109</v>
       </c>
       <c r="G77" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" s="0"/>
       <c r="I77" s="0" t="s">
         <v>113</v>
       </c>
       <c r="J77" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K77" s="0" t="s">
         <v>118</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="78">
@@ -2995,7 +2995,7 @@
         <v>39</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C79" s="0">
         <v>1</v>
@@ -3004,7 +3004,7 @@
         <v>48</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="F79" s="0" t="s">
         <v>109</v>
@@ -3020,10 +3020,10 @@
         <v>116</v>
       </c>
       <c r="K79" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L79" s="0" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="80">
@@ -3034,7 +3034,7 @@
         <v>2</v>
       </c>
       <c r="C80" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D80" s="0"/>
       <c r="E80" s="0"/>
@@ -3059,7 +3059,7 @@
         <v>40</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C81" s="0">
         <v>1</v>
@@ -3068,7 +3068,7 @@
         <v>49</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F81" s="0" t="s">
         <v>109</v>
@@ -3081,13 +3081,13 @@
         <v>113</v>
       </c>
       <c r="J81" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K81" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L81" s="0" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
     </row>
     <row r="82">
@@ -3132,7 +3132,7 @@
         <v>50</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>103</v>
+        <v>24</v>
       </c>
       <c r="F83" s="0" t="s">
         <v>109</v>
@@ -3148,10 +3148,10 @@
         <v>116</v>
       </c>
       <c r="K83" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L83" s="0" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="84">
@@ -3187,7 +3187,7 @@
         <v>42</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C85" s="0">
         <v>1</v>
@@ -3196,7 +3196,7 @@
         <v>51</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="F85" s="0" t="s">
         <v>109</v>
@@ -3209,13 +3209,13 @@
         <v>113</v>
       </c>
       <c r="J85" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K85" s="0" t="s">
         <v>119</v>
       </c>
       <c r="L85" s="0" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="86">
@@ -3251,7 +3251,7 @@
         <v>43</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C87" s="0">
         <v>1</v>
@@ -3260,7 +3260,7 @@
         <v>52</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F87" s="0" t="s">
         <v>109</v>
@@ -3273,13 +3273,13 @@
         <v>113</v>
       </c>
       <c r="J87" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K87" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L87" s="0" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="88">
@@ -3290,7 +3290,7 @@
         <v>2</v>
       </c>
       <c r="C88" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D88" s="0"/>
       <c r="E88" s="0"/>
@@ -3315,7 +3315,7 @@
         <v>44</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C89" s="0">
         <v>1</v>
@@ -3324,7 +3324,7 @@
         <v>53</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F89" s="0" t="s">
         <v>109</v>
@@ -3337,13 +3337,13 @@
         <v>113</v>
       </c>
       <c r="J89" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K89" s="0" t="s">
         <v>120</v>
       </c>
       <c r="L89" s="0" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
     </row>
     <row r="90">
@@ -3388,7 +3388,7 @@
         <v>54</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F91" s="0" t="s">
         <v>109</v>
@@ -3401,13 +3401,13 @@
         <v>113</v>
       </c>
       <c r="J91" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K91" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L91" s="0" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="92">
@@ -3443,7 +3443,7 @@
         <v>46</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C93" s="0">
         <v>1</v>
@@ -3468,10 +3468,10 @@
         <v>115</v>
       </c>
       <c r="K93" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L93" s="0" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="94">
@@ -3482,7 +3482,7 @@
         <v>2</v>
       </c>
       <c r="C94" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D94" s="0"/>
       <c r="E94" s="0"/>
@@ -3507,7 +3507,7 @@
         <v>47</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C95" s="0">
         <v>1</v>
@@ -3516,7 +3516,7 @@
         <v>56</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F95" s="0" t="s">
         <v>109</v>
@@ -3532,10 +3532,10 @@
         <v>116</v>
       </c>
       <c r="K95" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L95" s="0" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="96">
@@ -3571,7 +3571,7 @@
         <v>48</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C97" s="0">
         <v>1</v>
@@ -3580,7 +3580,7 @@
         <v>57</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="F97" s="0" t="s">
         <v>109</v>
@@ -3593,13 +3593,13 @@
         <v>113</v>
       </c>
       <c r="J97" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K97" s="0" t="s">
         <v>118</v>
       </c>
       <c r="L97" s="0" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="98">
@@ -3610,7 +3610,7 @@
         <v>2</v>
       </c>
       <c r="C98" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D98" s="0"/>
       <c r="E98" s="0"/>
@@ -3635,7 +3635,7 @@
         <v>49</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C99" s="0">
         <v>1</v>
@@ -3644,7 +3644,7 @@
         <v>58</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="F99" s="0" t="s">
         <v>109</v>
@@ -3663,7 +3663,7 @@
         <v>119</v>
       </c>
       <c r="L99" s="0" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
     <row r="100">
@@ -3674,7 +3674,7 @@
         <v>2</v>
       </c>
       <c r="C100" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D100" s="0"/>
       <c r="E100" s="0"/>
@@ -3699,7 +3699,7 @@
         <v>50</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C101" s="0">
         <v>1</v>
@@ -3708,7 +3708,7 @@
         <v>59</v>
       </c>
       <c r="E101" s="0" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="F101" s="0" t="s">
         <v>109</v>
@@ -3721,13 +3721,13 @@
         <v>113</v>
       </c>
       <c r="J101" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K101" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L101" s="0" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="102">
@@ -3763,7 +3763,7 @@
         <v>51</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C103" s="0">
         <v>1</v>
@@ -3788,10 +3788,10 @@
         <v>115</v>
       </c>
       <c r="K103" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L103" s="0" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
     </row>
     <row r="104">
@@ -3827,7 +3827,7 @@
         <v>52</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C105" s="0">
         <v>1</v>
@@ -3836,7 +3836,7 @@
         <v>61</v>
       </c>
       <c r="E105" s="0" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="F105" s="0" t="s">
         <v>109</v>
@@ -3849,13 +3849,13 @@
         <v>113</v>
       </c>
       <c r="J105" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K105" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L105" s="0" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="106">
@@ -3900,7 +3900,7 @@
         <v>62</v>
       </c>
       <c r="E107" s="0" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="F107" s="0" t="s">
         <v>109</v>
@@ -3916,10 +3916,10 @@
         <v>116</v>
       </c>
       <c r="K107" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L107" s="0" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="108">
@@ -3930,7 +3930,7 @@
         <v>2</v>
       </c>
       <c r="C108" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D108" s="0"/>
       <c r="E108" s="0"/>
@@ -3955,7 +3955,7 @@
         <v>54</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C109" s="0">
         <v>1</v>
@@ -3964,7 +3964,7 @@
         <v>63</v>
       </c>
       <c r="E109" s="0" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F109" s="0" t="s">
         <v>109</v>
@@ -3977,13 +3977,13 @@
         <v>113</v>
       </c>
       <c r="J109" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K109" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L109" s="0" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
     </row>
     <row r="110">
@@ -3994,7 +3994,7 @@
         <v>2</v>
       </c>
       <c r="C110" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D110" s="0"/>
       <c r="E110" s="0"/>
@@ -4019,7 +4019,7 @@
         <v>55</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C111" s="0">
         <v>1</v>
@@ -4044,10 +4044,10 @@
         <v>115</v>
       </c>
       <c r="K111" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L111" s="0" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="112">
@@ -4058,7 +4058,7 @@
         <v>2</v>
       </c>
       <c r="C112" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D112" s="0"/>
       <c r="E112" s="0"/>
@@ -4092,7 +4092,7 @@
         <v>65</v>
       </c>
       <c r="E113" s="0" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="F113" s="0" t="s">
         <v>109</v>
@@ -4105,13 +4105,13 @@
         <v>113</v>
       </c>
       <c r="J113" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K113" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L113" s="0" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="114">
@@ -4122,7 +4122,7 @@
         <v>2</v>
       </c>
       <c r="C114" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D114" s="0"/>
       <c r="E114" s="0"/>
@@ -4156,7 +4156,7 @@
         <v>66</v>
       </c>
       <c r="E115" s="0" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="F115" s="0" t="s">
         <v>109</v>
@@ -4169,13 +4169,13 @@
         <v>113</v>
       </c>
       <c r="J115" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K115" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L115" s="0" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="116">
@@ -4211,7 +4211,7 @@
         <v>58</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C117" s="0">
         <v>1</v>
@@ -4236,10 +4236,10 @@
         <v>115</v>
       </c>
       <c r="K117" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L117" s="0" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="118">
@@ -4250,7 +4250,7 @@
         <v>2</v>
       </c>
       <c r="C118" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D118" s="0"/>
       <c r="E118" s="0"/>
@@ -4275,7 +4275,7 @@
         <v>59</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C119" s="0">
         <v>1</v>
@@ -4284,7 +4284,7 @@
         <v>68</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="F119" s="0" t="s">
         <v>109</v>
@@ -4297,13 +4297,13 @@
         <v>113</v>
       </c>
       <c r="J119" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K119" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L119" s="0" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
     <row r="120">
@@ -4348,7 +4348,7 @@
         <v>69</v>
       </c>
       <c r="E121" s="0" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="F121" s="0" t="s">
         <v>109</v>
@@ -4361,10 +4361,10 @@
         <v>113</v>
       </c>
       <c r="J121" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K121" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L121" s="0" t="s">
         <v>129</v>
@@ -4378,7 +4378,7 @@
         <v>2</v>
       </c>
       <c r="C122" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D122" s="0"/>
       <c r="E122" s="0"/>
@@ -4412,7 +4412,7 @@
         <v>70</v>
       </c>
       <c r="E123" s="0" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="F123" s="0" t="s">
         <v>109</v>
@@ -4428,10 +4428,10 @@
         <v>116</v>
       </c>
       <c r="K123" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L123" s="0" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="124">
@@ -4442,7 +4442,7 @@
         <v>2</v>
       </c>
       <c r="C124" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D124" s="0"/>
       <c r="E124" s="0"/>
@@ -4467,7 +4467,7 @@
         <v>62</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C125" s="0">
         <v>1</v>
@@ -4476,7 +4476,7 @@
         <v>71</v>
       </c>
       <c r="E125" s="0" t="s">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="F125" s="0" t="s">
         <v>109</v>
@@ -4492,10 +4492,10 @@
         <v>116</v>
       </c>
       <c r="K125" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L125" s="0" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
     </row>
     <row r="126">
@@ -4506,7 +4506,7 @@
         <v>2</v>
       </c>
       <c r="C126" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D126" s="0"/>
       <c r="E126" s="0"/>
@@ -4531,7 +4531,7 @@
         <v>63</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C127" s="0">
         <v>1</v>
@@ -4540,7 +4540,7 @@
         <v>72</v>
       </c>
       <c r="E127" s="0" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="F127" s="0" t="s">
         <v>109</v>
@@ -4553,13 +4553,13 @@
         <v>113</v>
       </c>
       <c r="J127" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K127" s="0" t="s">
         <v>119</v>
       </c>
       <c r="L127" s="0" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="128">
@@ -4570,7 +4570,7 @@
         <v>2</v>
       </c>
       <c r="C128" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D128" s="0"/>
       <c r="E128" s="0"/>
@@ -4595,7 +4595,7 @@
         <v>64</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C129" s="0">
         <v>1</v>
@@ -4620,10 +4620,10 @@
         <v>115</v>
       </c>
       <c r="K129" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L129" s="0" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="130">
@@ -4634,7 +4634,7 @@
         <v>2</v>
       </c>
       <c r="C130" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D130" s="0"/>
       <c r="E130" s="0"/>
@@ -4668,7 +4668,7 @@
         <v>74</v>
       </c>
       <c r="E131" s="0" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F131" s="0" t="s">
         <v>109</v>
@@ -4681,13 +4681,13 @@
         <v>113</v>
       </c>
       <c r="J131" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K131" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L131" s="0" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="132">
@@ -4698,7 +4698,7 @@
         <v>2</v>
       </c>
       <c r="C132" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D132" s="0"/>
       <c r="E132" s="0"/>
@@ -4732,7 +4732,7 @@
         <v>75</v>
       </c>
       <c r="E133" s="0" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="F133" s="0" t="s">
         <v>109</v>
@@ -4745,10 +4745,10 @@
         <v>113</v>
       </c>
       <c r="J133" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K133" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L133" s="0" t="s">
         <v>126</v>
@@ -4762,7 +4762,7 @@
         <v>2</v>
       </c>
       <c r="C134" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D134" s="0"/>
       <c r="E134" s="0"/>
@@ -4787,7 +4787,7 @@
         <v>67</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C135" s="0">
         <v>1</v>
@@ -4812,10 +4812,10 @@
         <v>115</v>
       </c>
       <c r="K135" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L135" s="0" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="136">
@@ -4851,7 +4851,7 @@
         <v>68</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C137" s="0">
         <v>1</v>
@@ -4876,10 +4876,10 @@
         <v>115</v>
       </c>
       <c r="K137" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L137" s="0" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="138">
@@ -4890,7 +4890,7 @@
         <v>2</v>
       </c>
       <c r="C138" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D138" s="0"/>
       <c r="E138" s="0"/>
@@ -4915,7 +4915,7 @@
         <v>69</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C139" s="0">
         <v>1</v>
@@ -4940,10 +4940,10 @@
         <v>115</v>
       </c>
       <c r="K139" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L139" s="0" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="140">
@@ -4954,7 +4954,7 @@
         <v>2</v>
       </c>
       <c r="C140" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D140" s="0"/>
       <c r="E140" s="0"/>
@@ -4979,7 +4979,7 @@
         <v>70</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C141" s="0">
         <v>1</v>
@@ -4988,7 +4988,7 @@
         <v>79</v>
       </c>
       <c r="E141" s="0" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="F141" s="0" t="s">
         <v>109</v>
@@ -5001,13 +5001,13 @@
         <v>113</v>
       </c>
       <c r="J141" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K141" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L141" s="0" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="142">
@@ -5043,7 +5043,7 @@
         <v>71</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C143" s="0">
         <v>1</v>
@@ -5052,7 +5052,7 @@
         <v>80</v>
       </c>
       <c r="E143" s="0" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F143" s="0" t="s">
         <v>109</v>
@@ -5068,10 +5068,10 @@
         <v>116</v>
       </c>
       <c r="K143" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L143" s="0" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="144">
@@ -5107,7 +5107,7 @@
         <v>72</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C145" s="0">
         <v>1</v>
@@ -5116,7 +5116,7 @@
         <v>81</v>
       </c>
       <c r="E145" s="0" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="F145" s="0" t="s">
         <v>109</v>
@@ -5129,13 +5129,13 @@
         <v>113</v>
       </c>
       <c r="J145" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K145" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L145" s="0" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="146">
@@ -5171,7 +5171,7 @@
         <v>73</v>
       </c>
       <c r="B147" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C147" s="0">
         <v>1</v>
@@ -5180,7 +5180,7 @@
         <v>82</v>
       </c>
       <c r="E147" s="0" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F147" s="0" t="s">
         <v>109</v>
@@ -5193,13 +5193,13 @@
         <v>113</v>
       </c>
       <c r="J147" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K147" s="0" t="s">
         <v>118</v>
       </c>
       <c r="L147" s="0" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="148">
@@ -5235,7 +5235,7 @@
         <v>74</v>
       </c>
       <c r="B149" s="0" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C149" s="0">
         <v>1</v>
@@ -5244,7 +5244,7 @@
         <v>83</v>
       </c>
       <c r="E149" s="0" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="F149" s="0" t="s">
         <v>109</v>
@@ -5257,13 +5257,13 @@
         <v>113</v>
       </c>
       <c r="J149" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K149" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L149" s="0" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
     </row>
     <row r="150">
@@ -5299,7 +5299,7 @@
         <v>75</v>
       </c>
       <c r="B151" s="0" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C151" s="0">
         <v>1</v>
@@ -5324,10 +5324,10 @@
         <v>115</v>
       </c>
       <c r="K151" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L151" s="0" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="152">
@@ -5338,7 +5338,7 @@
         <v>2</v>
       </c>
       <c r="C152" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D152" s="0"/>
       <c r="E152" s="0"/>
@@ -5363,7 +5363,7 @@
         <v>76</v>
       </c>
       <c r="B153" s="0" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C153" s="0">
         <v>1</v>
@@ -5372,7 +5372,7 @@
         <v>85</v>
       </c>
       <c r="E153" s="0" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="F153" s="0" t="s">
         <v>109</v>
@@ -5388,10 +5388,10 @@
         <v>116</v>
       </c>
       <c r="K153" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L153" s="0" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="154">
@@ -5402,7 +5402,7 @@
         <v>2</v>
       </c>
       <c r="C154" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D154" s="0"/>
       <c r="E154" s="0"/>
@@ -5427,7 +5427,7 @@
         <v>77</v>
       </c>
       <c r="B155" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C155" s="0">
         <v>1</v>
@@ -5436,7 +5436,7 @@
         <v>86</v>
       </c>
       <c r="E155" s="0" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="F155" s="0" t="s">
         <v>109</v>
@@ -5449,13 +5449,13 @@
         <v>113</v>
       </c>
       <c r="J155" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K155" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L155" s="0" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="156">
@@ -5466,7 +5466,7 @@
         <v>2</v>
       </c>
       <c r="C156" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D156" s="0"/>
       <c r="E156" s="0"/>
@@ -5491,7 +5491,7 @@
         <v>78</v>
       </c>
       <c r="B157" s="0" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C157" s="0">
         <v>1</v>
@@ -5500,7 +5500,7 @@
         <v>87</v>
       </c>
       <c r="E157" s="0" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="F157" s="0" t="s">
         <v>109</v>
@@ -5513,13 +5513,13 @@
         <v>113</v>
       </c>
       <c r="J157" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K157" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L157" s="0" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="158">
@@ -5530,7 +5530,7 @@
         <v>2</v>
       </c>
       <c r="C158" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D158" s="0"/>
       <c r="E158" s="0"/>
@@ -5555,7 +5555,7 @@
         <v>79</v>
       </c>
       <c r="B159" s="0" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C159" s="0">
         <v>1</v>
@@ -5564,7 +5564,7 @@
         <v>88</v>
       </c>
       <c r="E159" s="0" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F159" s="0" t="s">
         <v>109</v>
@@ -5580,10 +5580,10 @@
         <v>116</v>
       </c>
       <c r="K159" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L159" s="0" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="160">
@@ -5594,7 +5594,7 @@
         <v>2</v>
       </c>
       <c r="C160" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D160" s="0"/>
       <c r="E160" s="0"/>
@@ -5619,7 +5619,7 @@
         <v>80</v>
       </c>
       <c r="B161" s="0" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C161" s="0">
         <v>1</v>
@@ -5644,10 +5644,10 @@
         <v>115</v>
       </c>
       <c r="K161" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L161" s="0" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="162">
@@ -5658,7 +5658,7 @@
         <v>2</v>
       </c>
       <c r="C162" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D162" s="0"/>
       <c r="E162" s="0"/>
@@ -5683,7 +5683,7 @@
         <v>81</v>
       </c>
       <c r="B163" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C163" s="0">
         <v>1</v>
@@ -5692,7 +5692,7 @@
         <v>90</v>
       </c>
       <c r="E163" s="0" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="F163" s="0" t="s">
         <v>109</v>
@@ -5708,10 +5708,10 @@
         <v>116</v>
       </c>
       <c r="K163" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L163" s="0" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
     </row>
     <row r="164">
@@ -5775,7 +5775,7 @@
         <v>119</v>
       </c>
       <c r="L165" s="0" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="166">
@@ -5811,35 +5811,35 @@
         <v>83</v>
       </c>
       <c r="B167" s="0" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C167" s="0">
         <v>1</v>
       </c>
       <c r="D167" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E167" s="0" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="F167" s="0" t="s">
         <v>109</v>
       </c>
       <c r="G167" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H167" s="0"/>
       <c r="I167" s="0" t="s">
         <v>113</v>
       </c>
       <c r="J167" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K167" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L167" s="0" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="168">
@@ -5850,7 +5850,7 @@
         <v>2</v>
       </c>
       <c r="C168" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D168" s="0"/>
       <c r="E168" s="0"/>
@@ -5875,16 +5875,16 @@
         <v>84</v>
       </c>
       <c r="B169" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C169" s="0">
         <v>1</v>
       </c>
       <c r="D169" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E169" s="0" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F169" s="0" t="s">
         <v>109</v>
@@ -5903,7 +5903,7 @@
         <v>120</v>
       </c>
       <c r="L169" s="0" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="170">
@@ -5914,7 +5914,7 @@
         <v>2</v>
       </c>
       <c r="C170" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D170" s="0"/>
       <c r="E170" s="0"/>
@@ -5939,16 +5939,16 @@
         <v>85</v>
       </c>
       <c r="B171" s="0" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C171" s="0">
         <v>1</v>
       </c>
       <c r="D171" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E171" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F171" s="0" t="s">
         <v>109</v>
@@ -5964,10 +5964,10 @@
         <v>115</v>
       </c>
       <c r="K171" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L171" s="0" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="172">
@@ -6003,16 +6003,16 @@
         <v>86</v>
       </c>
       <c r="B173" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C173" s="0">
         <v>1</v>
       </c>
       <c r="D173" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E173" s="0" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="F173" s="0" t="s">
         <v>109</v>
@@ -6031,7 +6031,7 @@
         <v>120</v>
       </c>
       <c r="L173" s="0" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="174">
@@ -6042,7 +6042,7 @@
         <v>2</v>
       </c>
       <c r="C174" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D174" s="0"/>
       <c r="E174" s="0"/>
@@ -6073,10 +6073,10 @@
         <v>1</v>
       </c>
       <c r="D175" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E175" s="0" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="F175" s="0" t="s">
         <v>109</v>
@@ -6089,13 +6089,13 @@
         <v>113</v>
       </c>
       <c r="J175" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K175" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L175" s="0" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="176">
@@ -6137,10 +6137,10 @@
         <v>1</v>
       </c>
       <c r="D177" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E177" s="0" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="F177" s="0" t="s">
         <v>109</v>
@@ -6156,10 +6156,10 @@
         <v>116</v>
       </c>
       <c r="K177" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L177" s="0" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="178">
@@ -6170,7 +6170,7 @@
         <v>2</v>
       </c>
       <c r="C178" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D178" s="0"/>
       <c r="E178" s="0"/>
@@ -6195,16 +6195,16 @@
         <v>89</v>
       </c>
       <c r="B179" s="0" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C179" s="0">
         <v>1</v>
       </c>
       <c r="D179" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E179" s="0" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="F179" s="0" t="s">
         <v>109</v>
@@ -6217,13 +6217,13 @@
         <v>113</v>
       </c>
       <c r="J179" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K179" s="0" t="s">
         <v>118</v>
       </c>
       <c r="L179" s="0" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="180">
@@ -6259,16 +6259,16 @@
         <v>90</v>
       </c>
       <c r="B181" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C181" s="0">
         <v>1</v>
       </c>
       <c r="D181" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E181" s="0" t="s">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="F181" s="0" t="s">
         <v>109</v>
@@ -6281,13 +6281,13 @@
         <v>113</v>
       </c>
       <c r="J181" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K181" s="0" t="s">
         <v>120</v>
       </c>
       <c r="L181" s="0" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
     </row>
     <row r="182">
@@ -6298,7 +6298,7 @@
         <v>2</v>
       </c>
       <c r="C182" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D182" s="0"/>
       <c r="E182" s="0"/>
@@ -6329,10 +6329,10 @@
         <v>1</v>
       </c>
       <c r="D183" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E183" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F183" s="0" t="s">
         <v>109</v>
@@ -6351,7 +6351,7 @@
         <v>119</v>
       </c>
       <c r="L183" s="0" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="184">
@@ -6387,16 +6387,16 @@
         <v>92</v>
       </c>
       <c r="B185" s="0" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C185" s="0">
         <v>1</v>
       </c>
       <c r="D185" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E185" s="0" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="F185" s="0" t="s">
         <v>109</v>
@@ -6409,13 +6409,13 @@
         <v>113</v>
       </c>
       <c r="J185" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K185" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L185" s="0" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="186">
@@ -6457,10 +6457,10 @@
         <v>1</v>
       </c>
       <c r="D187" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E187" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F187" s="0" t="s">
         <v>109</v>
@@ -6479,7 +6479,7 @@
         <v>119</v>
       </c>
       <c r="L187" s="0" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
     </row>
     <row r="188">
@@ -6515,7 +6515,7 @@
         <v>94</v>
       </c>
       <c r="B189" s="0" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C189" s="0">
         <v>1</v>
@@ -6524,26 +6524,26 @@
         <v>102</v>
       </c>
       <c r="E189" s="0" t="s">
-        <v>40</v>
+        <v>102</v>
       </c>
       <c r="F189" s="0" t="s">
         <v>109</v>
       </c>
       <c r="G189" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H189" s="0"/>
       <c r="I189" s="0" t="s">
         <v>113</v>
       </c>
       <c r="J189" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K189" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L189" s="0" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="190">
@@ -6554,7 +6554,7 @@
         <v>2</v>
       </c>
       <c r="C190" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D190" s="0"/>
       <c r="E190" s="0"/>
@@ -6579,7 +6579,7 @@
         <v>95</v>
       </c>
       <c r="B191" s="0" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C191" s="0">
         <v>1</v>
@@ -6604,10 +6604,10 @@
         <v>115</v>
       </c>
       <c r="K191" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L191" s="0" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
     </row>
     <row r="192">
@@ -6643,7 +6643,7 @@
         <v>96</v>
       </c>
       <c r="B193" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C193" s="0">
         <v>1</v>
@@ -6652,7 +6652,7 @@
         <v>104</v>
       </c>
       <c r="E193" s="0" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="F193" s="0" t="s">
         <v>109</v>
@@ -6707,7 +6707,7 @@
         <v>97</v>
       </c>
       <c r="B195" s="0" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C195" s="0">
         <v>1</v>
@@ -6716,7 +6716,7 @@
         <v>105</v>
       </c>
       <c r="E195" s="0" t="s">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="F195" s="0" t="s">
         <v>109</v>
@@ -6729,13 +6729,13 @@
         <v>113</v>
       </c>
       <c r="J195" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K195" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L195" s="0" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
     </row>
     <row r="196">
@@ -6746,7 +6746,7 @@
         <v>2</v>
       </c>
       <c r="C196" s="0">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D196" s="0"/>
       <c r="E196" s="0"/>
@@ -6771,7 +6771,7 @@
         <v>98</v>
       </c>
       <c r="B197" s="0" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C197" s="0">
         <v>1</v>
@@ -6780,7 +6780,7 @@
         <v>106</v>
       </c>
       <c r="E197" s="0" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="F197" s="0" t="s">
         <v>109</v>
@@ -6793,13 +6793,13 @@
         <v>113</v>
       </c>
       <c r="J197" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K197" s="0" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L197" s="0" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="198">
@@ -6810,7 +6810,7 @@
         <v>2</v>
       </c>
       <c r="C198" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D198" s="0"/>
       <c r="E198" s="0"/>
